--- a/z0bug_odoo/data/account_tax.xlsx
+++ b/z0bug_odoo/data/account_tax.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="345">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -190,6 +190,12 @@
     <t xml:space="preserve">external.153050</t>
   </si>
   <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">self</t>
+  </si>
+  <si>
     <t xml:space="preserve">external.aa17c2v</t>
   </si>
   <si>
@@ -226,12 +232,6 @@
     <t xml:space="preserve">l10n_it_account_tax_kind.n6_4</t>
   </si>
   <si>
-    <t xml:space="preserve">True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">local</t>
-  </si>
-  <si>
     <t xml:space="preserve">external.aa17c6v</t>
   </si>
   <si>
@@ -422,9 +422,6 @@
   </si>
   <si>
     <t xml:space="preserve">l10n_it_account_tax_kind.n2_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">self</t>
   </si>
   <si>
     <t xml:space="preserve">external.aa7v</t>
@@ -1298,7 +1295,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="21.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="7.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.2"/>
   </cols>
   <sheetData>
@@ -1696,20 +1693,25 @@
       <c r="L12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="O12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>200</v>
@@ -1727,21 +1729,21 @@
         <v>0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>24</v>
@@ -1759,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>48</v>
@@ -1771,13 +1773,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>25</v>
@@ -1801,13 +1803,13 @@
         <v>55</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>70</v>
@@ -1839,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1871,10 +1873,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1912,10 +1914,10 @@
         <v>80</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>81</v>
@@ -1947,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1979,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2020,10 +2022,10 @@
         <v>91</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>92</v>
@@ -2055,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,19 +2089,19 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>99</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2137,10 +2139,10 @@
         <v>99</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>103</v>
@@ -2172,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2204,19 +2206,19 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>99</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2284,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>48</v>
@@ -2320,10 +2322,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>48</v>
@@ -2356,19 +2358,19 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>123</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2397,19 +2399,19 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>123</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>127</v>
@@ -2474,24 +2476,24 @@
         <v>133</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="E34" s="1" t="n">
         <v>42</v>
@@ -2515,13 +2517,13 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>43</v>
@@ -2545,13 +2547,13 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>44</v>
@@ -2575,13 +2577,13 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="E37" s="1" t="n">
         <v>45</v>
@@ -2605,27 +2607,27 @@
         <v>55</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="E38" s="1" t="n">
         <v>200</v>
@@ -2649,19 +2651,19 @@
         <v>55</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>46</v>
@@ -2685,19 +2687,19 @@
         <v>55</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E40" s="1" t="n">
         <v>47</v>
@@ -2715,19 +2717,19 @@
         <v>0</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="E41" s="1" t="n">
         <v>48</v>
@@ -2745,19 +2747,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="E42" s="1" t="n">
         <v>51</v>
@@ -2775,27 +2777,27 @@
         <v>0</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E43" s="1" t="n">
         <v>52</v>
@@ -2813,19 +2815,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>55</v>
@@ -2843,19 +2845,19 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>56</v>
@@ -2873,19 +2875,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>57</v>
@@ -2903,19 +2905,19 @@
         <v>0</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>58</v>
@@ -2933,19 +2935,19 @@
         <v>0</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="E48" s="1" t="n">
         <v>59</v>
@@ -2969,13 +2971,13 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="E49" s="1" t="n">
         <v>60</v>
@@ -2999,13 +3001,13 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="E50" s="1" t="n">
         <v>65</v>
@@ -3029,13 +3031,13 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>66</v>
@@ -3059,13 +3061,13 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>69</v>
@@ -3089,13 +3091,13 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="E53" s="1" t="n">
         <v>70</v>
@@ -3119,13 +3121,13 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E54" s="1" t="n">
         <v>71</v>
@@ -3143,24 +3145,24 @@
         <v>0</v>
       </c>
       <c r="J54" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P54" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>72</v>
@@ -3178,24 +3180,24 @@
         <v>0</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="E56" s="1" t="n">
         <v>73</v>
@@ -3215,13 +3217,13 @@
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="E57" s="1" t="n">
         <v>74</v>
@@ -3241,13 +3243,13 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="E58" s="1" t="n">
         <v>77</v>
@@ -3267,13 +3269,13 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="E59" s="1" t="n">
         <v>78</v>
@@ -3293,13 +3295,13 @@
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="D60" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="E60" s="1" t="n">
         <v>79</v>
@@ -3319,13 +3321,13 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="E61" s="1" t="n">
         <v>80</v>
@@ -3345,13 +3347,13 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="E62" s="1" t="n">
         <v>85</v>
@@ -3371,13 +3373,13 @@
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>86</v>
@@ -3397,13 +3399,13 @@
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="E64" s="1" t="n">
         <v>87</v>
@@ -3423,13 +3425,13 @@
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="D65" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="E65" s="1" t="n">
         <v>88</v>
@@ -3449,13 +3451,13 @@
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="D66" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>89</v>
@@ -3475,13 +3477,13 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="E67" s="1" t="n">
         <v>90</v>
@@ -3501,13 +3503,13 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="D68" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="E68" s="1" t="n">
         <v>91</v>
@@ -3533,13 +3535,13 @@
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="E69" s="1" t="n">
         <v>92</v>
@@ -3565,13 +3567,13 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="E70" s="1" t="n">
         <v>93</v>
@@ -3597,13 +3599,13 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="E71" s="1" t="n">
         <v>100</v>
@@ -3623,13 +3625,13 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="E72" s="1" t="n">
         <v>100</v>
@@ -3649,25 +3651,25 @@
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="D73" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="E73" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="I73" s="1" t="n">
         <v>0</v>
@@ -3675,13 +3677,13 @@
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="E74" s="1" t="n">
         <v>100</v>
@@ -3701,19 +3703,19 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="D75" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="E75" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>19</v>
@@ -3727,25 +3729,25 @@
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="E76" s="1" t="n">
         <v>100</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I76" s="1" t="n">
         <v>0</v>
@@ -3753,13 +3755,13 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="E77" s="1" t="n">
         <v>100</v>
@@ -3779,13 +3781,13 @@
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="E78" s="1" t="n">
         <v>100</v>
@@ -3805,13 +3807,13 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="E79" s="1" t="n">
         <v>100</v>
@@ -3831,13 +3833,13 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="E80" s="1" t="n">
         <v>200</v>
@@ -3863,13 +3865,13 @@
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="D81" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="E81" s="1" t="n">
         <v>200</v>
@@ -3895,25 +3897,25 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="D82" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="E82" s="1" t="n">
         <v>200</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I82" s="1" t="n">
         <v>0</v>
@@ -3927,13 +3929,13 @@
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="D83" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="E83" s="1" t="n">
         <v>200</v>
@@ -3959,19 +3961,19 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="D84" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="E84" s="1" t="n">
         <v>200</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>19</v>
@@ -3991,25 +3993,25 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="D85" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="E85" s="1" t="n">
         <v>200</v>
       </c>
       <c r="F85" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="I85" s="1" t="n">
         <v>0</v>
@@ -4023,13 +4025,13 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="E86" s="1" t="n">
         <v>200</v>
@@ -4055,13 +4057,13 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="D87" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="E87" s="1" t="n">
         <v>200</v>
@@ -4087,13 +4089,13 @@
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C88" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="D88" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="E88" s="1" t="n">
         <v>200</v>
@@ -4119,13 +4121,13 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="E89" s="1" t="n">
         <v>10</v>
@@ -4134,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>25</v>
@@ -4145,13 +4147,13 @@
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="E90" s="1" t="n">
         <v>11</v>
@@ -4160,7 +4162,7 @@
         <v>10</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>25</v>
@@ -4171,13 +4173,13 @@
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="E91" s="1" t="n">
         <v>12</v>
@@ -4186,7 +4188,7 @@
         <v>4</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>25</v>
@@ -4197,13 +4199,13 @@
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C92" s="4" t="n">
         <v>2250</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E92" s="1" t="n">
         <v>13</v>
@@ -4212,7 +4214,7 @@
         <v>22</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>25</v>
@@ -4223,13 +4225,13 @@
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C93" s="4" t="n">
         <v>2220</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E93" s="1" t="n">
         <v>14</v>
@@ -4238,7 +4240,7 @@
         <v>22</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>25</v>
@@ -4249,13 +4251,13 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C94" s="4" t="n">
         <v>2280</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E94" s="1" t="n">
         <v>15</v>
@@ -4264,7 +4266,7 @@
         <v>22</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>25</v>
@@ -4275,13 +4277,13 @@
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C95" s="4" t="n">
         <v>2270</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E95" s="1" t="n">
         <v>16</v>
@@ -4290,7 +4292,7 @@
         <v>22</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>25</v>
@@ -4301,13 +4303,13 @@
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C96" s="4" t="n">
         <v>1050</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E96" s="1" t="n">
         <v>17</v>
@@ -4316,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>25</v>
@@ -4327,13 +4329,13 @@
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C97" s="4" t="n">
         <v>450</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>18</v>
@@ -4342,7 +4344,7 @@
         <v>4</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>25</v>
@@ -4353,13 +4355,13 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="D98" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="E98" s="1" t="n">
         <v>18</v>
@@ -4377,27 +4379,27 @@
         <v>0</v>
       </c>
       <c r="J98" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="P98" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P98" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E99" s="1" t="n">
         <v>18</v>
@@ -4415,13 +4417,13 @@
         <v>0</v>
       </c>
       <c r="J99" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="P99" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
   </sheetData>
